--- a/doc/SOC-_MCU TCP报文.xlsx
+++ b/doc/SOC-_MCU TCP报文.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
   <si>
     <t xml:space="preserve">  </t>
   </si>
@@ -142,7 +142,7 @@
     <t xml:space="preserve">依CMD而定</t>
   </si>
   <si>
-    <t xml:space="preserve">说明：运动指令/心跳指令 的应答</t>
+    <t xml:space="preserve">说明：OTA数据包/运动指令/心跳指令 的应答</t>
   </si>
   <si>
     <t xml:space="preserve">DATA子包#0   (n+3字节)</t>
@@ -326,6 +326,12 @@
     <t xml:space="preserve">p0 (小端)</t>
   </si>
   <si>
+    <t xml:space="preserve">Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0x01 OTA前查询/0x02 OTA全部发送完成后的通知</t>
+  </si>
+  <si>
     <t xml:space="preserve">8~9</t>
   </si>
   <si>
@@ -360,10 +366,10 @@
     <t xml:space="preserve">19~20</t>
   </si>
   <si>
+    <t xml:space="preserve">21~22</t>
+  </si>
+  <si>
     <t xml:space="preserve">0x0B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21~22</t>
   </si>
   <si>
     <t xml:space="preserve">23~24</t>
@@ -841,9 +847,6 @@
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -858,6 +861,9 @@
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
@@ -1206,11 +1212,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="19"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" max="12" min="12" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" max="13" min="13" style="0" width="77"/>
     <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" max="6" min="6" style="0" width="72"/>
     <col collapsed="false" customWidth="true" hidden="false" max="9" min="9" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="12" min="12" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1782,7 +1788,7 @@
       <c r="J20" s="10"/>
       <c r="K20" s="21"/>
       <c r="L20" s="26"/>
-      <c r="M20" s="29" t="s">
+      <c r="M20" s="7" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1801,19 +1807,19 @@
       <c r="F21" s="27"/>
       <c r="G21" s="5"/>
       <c r="H21" s="15"/>
-      <c r="I21" s="30">
+      <c r="I21" s="29">
         <v>9</v>
       </c>
-      <c r="J21" s="30">
-        <v>1</v>
-      </c>
-      <c r="K21" s="31" t="s">
+      <c r="J21" s="29">
+        <v>1</v>
+      </c>
+      <c r="K21" s="30" t="s">
         <v>11</v>
       </c>
       <c r="L21" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="M21" s="32" t="s">
+      <c r="M21" s="31" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1852,7 +1858,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="G23" s="33"/>
+      <c r="G23" s="32"/>
       <c r="H23" s="15"/>
       <c r="I23" s="21" t="s">
         <v>65</v>
@@ -1871,13 +1877,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="33"/>
-      <c r="B24" s="33"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
+      <c r="A24" s="32"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
       <c r="H24" s="15"/>
       <c r="I24" s="21" t="s">
         <v>67</v>
@@ -1904,7 +1910,7 @@
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="4"/>
-      <c r="G25" s="33"/>
+      <c r="G25" s="32"/>
       <c r="H25" s="15"/>
       <c r="I25" s="21" t="s">
         <v>70</v>
@@ -1918,8 +1924,8 @@
       <c r="L25" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="M25" s="34"/>
-      <c r="N25" s="33"/>
+      <c r="M25" s="33"/>
+      <c r="N25" s="32"/>
     </row>
     <row r="26">
       <c r="A26" s="24"/>
@@ -1938,7 +1944,7 @@
       <c r="F26" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="G26" s="33"/>
+      <c r="G26" s="32"/>
       <c r="H26" s="15"/>
       <c r="I26" s="21" t="s">
         <v>72</v>
@@ -1955,7 +1961,7 @@
       <c r="M26" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="N26" s="33"/>
+      <c r="N26" s="32"/>
     </row>
     <row r="27">
       <c r="A27" s="15" t="s">
@@ -1976,8 +1982,8 @@
       <c r="F27" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="G27" s="33"/>
-      <c r="N27" s="33"/>
+      <c r="G27" s="32"/>
+      <c r="N27" s="32"/>
     </row>
     <row r="28">
       <c r="A28" s="15"/>
@@ -1996,7 +2002,7 @@
       <c r="F28" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="G28" s="33"/>
+      <c r="G28" s="32"/>
       <c r="H28" s="6" t="s">
         <v>77</v>
       </c>
@@ -2005,7 +2011,7 @@
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="4"/>
-      <c r="N28" s="33"/>
+      <c r="N28" s="32"/>
     </row>
     <row r="29">
       <c r="A29" s="15"/>
@@ -2024,7 +2030,7 @@
       <c r="F29" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="G29" s="33"/>
+      <c r="G29" s="32"/>
       <c r="H29" s="7"/>
       <c r="I29" s="8" t="s">
         <v>5</v>
@@ -2041,7 +2047,7 @@
       <c r="M29" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="N29" s="33"/>
+      <c r="N29" s="32"/>
     </row>
     <row r="30">
       <c r="A30" s="15"/>
@@ -2060,7 +2066,7 @@
       <c r="F30" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="32"/>
       <c r="H30" s="9" t="s">
         <v>10</v>
       </c>
@@ -2079,7 +2085,7 @@
       <c r="M30" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N30" s="33"/>
+      <c r="N30" s="32"/>
     </row>
     <row r="31">
       <c r="A31" s="15"/>
@@ -2098,7 +2104,7 @@
       <c r="F31" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="G31" s="33"/>
+      <c r="G31" s="32"/>
       <c r="H31" s="9"/>
       <c r="I31" s="10">
         <v>1</v>
@@ -2115,7 +2121,7 @@
       <c r="M31" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="N31" s="33"/>
+      <c r="N31" s="32"/>
     </row>
     <row r="32">
       <c r="A32" s="15"/>
@@ -2134,7 +2140,7 @@
       <c r="F32" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="32"/>
       <c r="H32" s="13" t="s">
         <v>19</v>
       </c>
@@ -2153,15 +2159,15 @@
       <c r="M32" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="N32" s="33"/>
+      <c r="N32" s="32"/>
     </row>
     <row r="33">
-      <c r="A33" s="33"/>
-      <c r="B33" s="33"/>
-      <c r="C33" s="33"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
+      <c r="A33" s="32"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
       <c r="H33" s="15" t="s">
         <v>23</v>
       </c>
@@ -2180,7 +2186,7 @@
       <c r="M33" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="N33" s="33"/>
+      <c r="N33" s="32"/>
     </row>
     <row customHeight="true" ht="19" r="34">
       <c r="A34" s="2" t="s">
@@ -2207,7 +2213,7 @@
       <c r="M34" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="N34" s="33"/>
+      <c r="N34" s="32"/>
     </row>
     <row customHeight="true" ht="19" r="35">
       <c r="A35" s="24"/>
@@ -2240,7 +2246,7 @@
       <c r="M35" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="N35" s="33"/>
+      <c r="N35" s="32"/>
     </row>
     <row customHeight="true" ht="19" r="36">
       <c r="A36" s="15" t="s">
@@ -2275,26 +2281,28 @@
       <c r="M36" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="N36" s="33"/>
+      <c r="N36" s="32"/>
     </row>
     <row customHeight="true" ht="19" r="37">
       <c r="A37" s="15"/>
-      <c r="B37" s="21" t="s">
-        <v>52</v>
+      <c r="B37" s="10">
+        <v>1</v>
       </c>
       <c r="C37" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E37" s="21"/>
-      <c r="F37" s="27" t="s">
-        <v>53</v>
+        <v>11</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="F37" s="34" t="s">
+        <v>93</v>
       </c>
       <c r="H37" s="15"/>
       <c r="I37" s="10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J37" s="10">
         <v>2</v>
@@ -2304,26 +2312,26 @@
       </c>
       <c r="L37" s="21"/>
       <c r="M37" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="N37" s="33"/>
+        <v>95</v>
+      </c>
+      <c r="N37" s="32"/>
     </row>
     <row customHeight="true" ht="19" r="38">
       <c r="A38" s="15"/>
-      <c r="B38" s="21" t="s">
-        <v>55</v>
+      <c r="B38" s="10">
+        <v>2</v>
       </c>
       <c r="C38" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="E38" s="21"/>
       <c r="F38" s="27"/>
       <c r="H38" s="15"/>
       <c r="I38" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J38" s="10">
         <v>2</v>
@@ -2333,14 +2341,14 @@
       </c>
       <c r="L38" s="21"/>
       <c r="M38" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="N38" s="33"/>
+        <v>97</v>
+      </c>
+      <c r="N38" s="32"/>
     </row>
     <row customHeight="true" ht="19" r="39">
       <c r="A39" s="15"/>
       <c r="B39" s="21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C39" s="10">
         <v>2</v>
@@ -2352,7 +2360,7 @@
       <c r="F39" s="27"/>
       <c r="H39" s="15"/>
       <c r="I39" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J39" s="10">
         <v>2</v>
@@ -2362,14 +2370,14 @@
       </c>
       <c r="L39" s="21"/>
       <c r="M39" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="N39" s="33"/>
+        <v>99</v>
+      </c>
+      <c r="N39" s="32"/>
     </row>
     <row customHeight="true" ht="19" r="40">
       <c r="A40" s="15"/>
       <c r="B40" s="21" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C40" s="10">
         <v>2</v>
@@ -2391,14 +2399,14 @@
       </c>
       <c r="L40" s="21"/>
       <c r="M40" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="N40" s="33"/>
+        <v>100</v>
+      </c>
+      <c r="N40" s="32"/>
     </row>
     <row customHeight="true" ht="19" r="41">
       <c r="A41" s="15"/>
       <c r="B41" s="21" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C41" s="10">
         <v>2</v>
@@ -2419,14 +2427,26 @@
         <v>11</v>
       </c>
       <c r="L41" s="21" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M41" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="N41" s="33"/>
+      <c r="N41" s="32"/>
     </row>
     <row customHeight="true" ht="19" r="42">
+      <c r="A42" s="15"/>
+      <c r="B42" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" s="10">
+        <v>2</v>
+      </c>
+      <c r="D42" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E42" s="21"/>
+      <c r="F42" s="27"/>
       <c r="H42" s="15"/>
       <c r="I42" s="10">
         <v>16</v>
@@ -2439,20 +2459,11 @@
       </c>
       <c r="L42" s="21"/>
       <c r="M42" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="N42" s="33"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="33"/>
+        <v>102</v>
+      </c>
+      <c r="N42" s="32"/>
+    </row>
+    <row customHeight="true" ht="19" r="43">
       <c r="H43" s="15"/>
       <c r="I43" s="10" t="s">
         <v>72</v>
@@ -2467,28 +2478,21 @@
       <c r="M43" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="N43" s="33"/>
+      <c r="N43" s="32"/>
     </row>
     <row r="44">
-      <c r="A44" s="24"/>
-      <c r="B44" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="C44" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D44" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E44" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" s="25" t="s">
-        <v>9</v>
-      </c>
+      <c r="A44" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="32"/>
       <c r="H44" s="15"/>
       <c r="I44" s="10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="J44" s="10">
         <v>2</v>
@@ -2498,32 +2502,30 @@
       </c>
       <c r="L44" s="21"/>
       <c r="M44" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="N44" s="33"/>
+        <v>95</v>
+      </c>
+      <c r="N44" s="32"/>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B45" s="10">
-        <v>0</v>
-      </c>
-      <c r="C45" s="10">
-        <v>1</v>
-      </c>
-      <c r="D45" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="E45" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="F45" s="21" t="s">
-        <v>103</v>
+      <c r="A45" s="24"/>
+      <c r="B45" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E45" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="25" t="s">
+        <v>9</v>
       </c>
       <c r="H45" s="15"/>
       <c r="I45" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J45" s="10">
         <v>2</v>
@@ -2533,30 +2535,32 @@
       </c>
       <c r="L45" s="21"/>
       <c r="M45" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="N45" s="33"/>
+        <v>97</v>
+      </c>
+      <c r="N45" s="32"/>
     </row>
     <row r="46">
-      <c r="A46" s="15"/>
-      <c r="B46" s="21" t="s">
-        <v>52</v>
+      <c r="A46" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B46" s="10">
+        <v>0</v>
       </c>
       <c r="C46" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E46" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="F46" s="27" t="s">
-        <v>53</v>
+        <v>11</v>
+      </c>
+      <c r="E46" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="F46" s="21" t="s">
+        <v>106</v>
       </c>
       <c r="H46" s="15"/>
       <c r="I46" s="10" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J46" s="10">
         <v>2</v>
@@ -2566,14 +2570,14 @@
       </c>
       <c r="L46" s="21"/>
       <c r="M46" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="N46" s="33"/>
+        <v>99</v>
+      </c>
+      <c r="N46" s="32"/>
     </row>
     <row r="47">
       <c r="A47" s="15"/>
       <c r="B47" s="21" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C47" s="10">
         <v>2</v>
@@ -2581,8 +2585,12 @@
       <c r="D47" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="E47" s="27"/>
-      <c r="F47" s="27"/>
+      <c r="E47" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="F47" s="27" t="s">
+        <v>53</v>
+      </c>
       <c r="H47" s="15"/>
       <c r="I47" s="18">
         <v>25</v>
@@ -2594,15 +2602,15 @@
         <v>11</v>
       </c>
       <c r="L47" s="21"/>
-      <c r="M47" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="N47" s="33"/>
+      <c r="M47" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="N47" s="32"/>
     </row>
     <row r="48">
       <c r="A48" s="15"/>
       <c r="B48" s="21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C48" s="10">
         <v>2</v>
@@ -2614,24 +2622,24 @@
       <c r="F48" s="27"/>
       <c r="H48" s="15"/>
       <c r="I48" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J48" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="K48" s="34"/>
+        <v>109</v>
+      </c>
+      <c r="K48" s="33"/>
       <c r="L48" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M48" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="N48" s="33"/>
+        <v>111</v>
+      </c>
+      <c r="N48" s="32"/>
     </row>
     <row r="49">
       <c r="A49" s="15"/>
       <c r="B49" s="21" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C49" s="10">
         <v>2</v>
@@ -2641,16 +2649,12 @@
       </c>
       <c r="E49" s="27"/>
       <c r="F49" s="27"/>
-      <c r="I49" s="33"/>
-      <c r="J49" s="33"/>
-      <c r="K49" s="33"/>
-      <c r="L49" s="33"/>
-      <c r="M49" s="33"/>
+      <c r="N49" s="32"/>
     </row>
     <row r="50">
       <c r="A50" s="15"/>
       <c r="B50" s="21" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C50" s="10">
         <v>2</v>
@@ -2660,85 +2664,86 @@
       </c>
       <c r="E50" s="27"/>
       <c r="F50" s="27"/>
+      <c r="I50" s="32"/>
+      <c r="J50" s="32"/>
+      <c r="K50" s="32"/>
+      <c r="L50" s="32"/>
+      <c r="M50" s="32"/>
     </row>
     <row r="51">
-      <c r="A51" s="33"/>
-      <c r="B51" s="33"/>
-      <c r="C51" s="33"/>
-      <c r="D51" s="33"/>
-      <c r="E51" s="33"/>
-      <c r="F51" s="33"/>
+      <c r="A51" s="15"/>
+      <c r="B51" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C51" s="10">
+        <v>2</v>
+      </c>
+      <c r="D51" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E51" s="27"/>
+      <c r="F51" s="27"/>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="4"/>
+      <c r="A52" s="32"/>
+      <c r="B52" s="32"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="32"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="32"/>
     </row>
     <row r="53">
-      <c r="A53" s="24"/>
-      <c r="B53" s="25" t="s">
+      <c r="A53" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="4"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="24"/>
+      <c r="B54" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C53" s="25" t="s">
+      <c r="C54" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="D53" s="25" t="s">
+      <c r="D54" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E53" s="25" t="s">
+      <c r="E54" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="F53" s="25" t="s">
+      <c r="F54" s="25" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="15" t="s">
+    <row r="55">
+      <c r="A55" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B54" s="10">
+      <c r="B55" s="10">
         <v>0</v>
       </c>
-      <c r="C54" s="10">
-        <v>1</v>
-      </c>
-      <c r="D54" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="E54" s="21" t="s">
+      <c r="C55" s="10">
+        <v>1</v>
+      </c>
+      <c r="D55" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="F54" s="21" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="15"/>
-      <c r="B55" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="C55" s="10">
-        <v>2</v>
-      </c>
-      <c r="D55" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E55" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="F55" s="27" t="s">
-        <v>53</v>
+      <c r="F55" s="21" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="15"/>
       <c r="B56" s="21" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C56" s="10">
         <v>2</v>
@@ -2746,13 +2751,17 @@
       <c r="D56" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="E56" s="27"/>
-      <c r="F56" s="27"/>
+      <c r="E56" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="F56" s="27" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="15"/>
       <c r="B57" s="21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C57" s="10">
         <v>2</v>
@@ -2766,7 +2775,7 @@
     <row r="58">
       <c r="A58" s="15"/>
       <c r="B58" s="21" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C58" s="10">
         <v>2</v>
@@ -2780,7 +2789,7 @@
     <row r="59">
       <c r="A59" s="15"/>
       <c r="B59" s="21" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C59" s="10">
         <v>2</v>
@@ -2791,68 +2800,64 @@
       <c r="E59" s="27"/>
       <c r="F59" s="27"/>
     </row>
-    <row r="60"/>
-    <row r="61">
-      <c r="A61" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="4"/>
-    </row>
+    <row r="60">
+      <c r="A60" s="15"/>
+      <c r="B60" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C60" s="10">
+        <v>2</v>
+      </c>
+      <c r="D60" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E60" s="27"/>
+      <c r="F60" s="27"/>
+    </row>
+    <row r="61"/>
     <row r="62">
-      <c r="A62" s="24"/>
-      <c r="B62" s="25" t="s">
+      <c r="A62" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="4"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="24"/>
+      <c r="B63" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C62" s="25" t="s">
+      <c r="C63" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="D62" s="25" t="s">
+      <c r="D63" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E62" s="25" t="s">
+      <c r="E63" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="F62" s="25" t="s">
+      <c r="F63" s="25" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="15" t="s">
+    <row r="64">
+      <c r="A64" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B63" s="10">
+      <c r="B64" s="10">
         <v>0</v>
       </c>
-      <c r="C63" s="10">
-        <v>1</v>
-      </c>
-      <c r="D63" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="E63" s="21" t="s">
+      <c r="C64" s="10">
+        <v>1</v>
+      </c>
+      <c r="D64" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" s="21" t="s">
         <v>48</v>
-      </c>
-      <c r="F63" s="21" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="15"/>
-      <c r="B64" s="10">
-        <v>1</v>
-      </c>
-      <c r="C64" s="10">
-        <v>1</v>
-      </c>
-      <c r="D64" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="E64" s="21" t="s">
-        <v>114</v>
       </c>
       <c r="F64" s="21" t="s">
         <v>115</v>
@@ -2860,26 +2865,26 @@
     </row>
     <row r="65">
       <c r="A65" s="15"/>
-      <c r="B65" s="21" t="s">
+      <c r="B65" s="10">
+        <v>1</v>
+      </c>
+      <c r="C65" s="10">
+        <v>1</v>
+      </c>
+      <c r="D65" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="C65" s="10">
-        <v>2</v>
-      </c>
-      <c r="D65" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E65" s="21" t="s">
+      <c r="F65" s="21" t="s">
         <v>117</v>
-      </c>
-      <c r="F65" s="21" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="15"/>
       <c r="B66" s="21" t="s">
-        <v>34</v>
+        <v>118</v>
       </c>
       <c r="C66" s="10">
         <v>2</v>
@@ -2891,13 +2896,13 @@
         <v>119</v>
       </c>
       <c r="F66" s="21" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="15"/>
       <c r="B67" s="21" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C67" s="10">
         <v>2</v>
@@ -2906,131 +2911,131 @@
         <v>35</v>
       </c>
       <c r="E67" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="F67" s="21" t="s">
         <v>120</v>
-      </c>
-      <c r="F67" s="21" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="15"/>
-      <c r="B68" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="C68" s="18">
-        <v>2</v>
-      </c>
-      <c r="D68" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="E68" s="19" t="s">
+      <c r="B68" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C68" s="10">
+        <v>2</v>
+      </c>
+      <c r="D68" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E68" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="F68" s="19" t="s">
-        <v>121</v>
+      <c r="F68" s="21" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="15"/>
-      <c r="B69" s="18">
+      <c r="B69" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="C69" s="18">
+        <v>2</v>
+      </c>
+      <c r="D69" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="E69" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="F69" s="19" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="15"/>
+      <c r="B70" s="18">
         <v>10</v>
       </c>
-      <c r="C69" s="18">
-        <v>1</v>
-      </c>
-      <c r="D69" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E69" s="19" t="s">
+      <c r="C70" s="18">
+        <v>1</v>
+      </c>
+      <c r="D70" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F69" s="19" t="s">
+      <c r="F70" s="19" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="B70" s="34"/>
-      <c r="C70" s="34"/>
-      <c r="D70" s="34"/>
-      <c r="E70" s="34"/>
-      <c r="F70" s="34"/>
-    </row>
-    <row customHeight="true" ht="19" r="71"/>
-    <row r="72">
-      <c r="A72" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B72" s="3"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="4"/>
-    </row>
+    <row r="71">
+      <c r="A71" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="B71" s="33"/>
+      <c r="C71" s="33"/>
+      <c r="D71" s="33"/>
+      <c r="E71" s="33"/>
+      <c r="F71" s="33"/>
+    </row>
+    <row customHeight="true" ht="19" r="72"/>
     <row r="73">
-      <c r="A73" s="24"/>
-      <c r="B73" s="25" t="s">
+      <c r="A73" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="4"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="24"/>
+      <c r="B74" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C73" s="25" t="s">
+      <c r="C74" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="D73" s="25" t="s">
+      <c r="D74" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E73" s="25" t="s">
+      <c r="E74" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="F73" s="25" t="s">
+      <c r="F74" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="N73" s="33"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="15" t="s">
+      <c r="N74" s="32"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B74" s="10">
+      <c r="B75" s="10">
         <v>0</v>
       </c>
-      <c r="C74" s="10">
-        <v>1</v>
-      </c>
-      <c r="D74" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="E74" s="21" t="s">
+      <c r="C75" s="10">
+        <v>1</v>
+      </c>
+      <c r="D75" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E75" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="F74" s="21" t="s">
+      <c r="F75" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="N74" s="33"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="15"/>
-      <c r="B75" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="C75" s="10">
-        <v>2</v>
-      </c>
-      <c r="D75" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E75" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="F75" s="27" t="s">
-        <v>53</v>
-      </c>
+      <c r="N75" s="32"/>
     </row>
     <row r="76">
       <c r="A76" s="15"/>
       <c r="B76" s="21" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C76" s="10">
         <v>2</v>
@@ -3038,13 +3043,17 @@
       <c r="D76" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="E76" s="27"/>
-      <c r="F76" s="27"/>
+      <c r="E76" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="F76" s="27" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="15"/>
       <c r="B77" s="21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C77" s="10">
         <v>2</v>
@@ -3058,7 +3067,7 @@
     <row r="78">
       <c r="A78" s="15"/>
       <c r="B78" s="21" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C78" s="10">
         <v>2</v>
@@ -3071,68 +3080,69 @@
     </row>
     <row r="79">
       <c r="A79" s="15"/>
-      <c r="B79" s="19" t="s">
+      <c r="B79" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C79" s="10">
+        <v>2</v>
+      </c>
+      <c r="D79" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E79" s="27"/>
+      <c r="F79" s="27"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="15"/>
+      <c r="B80" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="C79" s="18">
-        <v>2</v>
-      </c>
-      <c r="D79" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="E79" s="37"/>
-      <c r="F79" s="37"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B80" s="3"/>
-      <c r="C80" s="3"/>
-      <c r="D80" s="3"/>
-      <c r="E80" s="3"/>
-      <c r="F80" s="4"/>
-    </row>
-    <row r="81"/>
-    <row r="82">
-      <c r="A82" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B82" s="3"/>
-      <c r="C82" s="3"/>
-      <c r="D82" s="3"/>
-      <c r="E82" s="4"/>
-    </row>
+      <c r="C80" s="18">
+        <v>2</v>
+      </c>
+      <c r="D80" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="E80" s="37"/>
+      <c r="F80" s="37"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="4"/>
+    </row>
+    <row r="82"/>
     <row r="83">
-      <c r="A83" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="B83" s="39" t="s">
+      <c r="A83" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C83" s="40" t="s">
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="4"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="D83" s="40"/>
-      <c r="E83" s="40"/>
-      <c r="N83" s="33"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="10">
-        <v>0</v>
-      </c>
-      <c r="B84" s="10" t="s">
+      <c r="B84" s="39" t="s">
         <v>130</v>
       </c>
-      <c r="C84" s="21" t="s">
+      <c r="C84" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="D84" s="21"/>
-      <c r="E84" s="21"/>
+      <c r="D84" s="40"/>
+      <c r="E84" s="40"/>
+      <c r="N84" s="32"/>
     </row>
     <row r="85">
       <c r="A85" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B85" s="10" t="s">
         <v>132</v>
@@ -3145,7 +3155,7 @@
     </row>
     <row r="86">
       <c r="A86" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B86" s="10" t="s">
         <v>134</v>
@@ -3158,23 +3168,23 @@
     </row>
     <row r="87">
       <c r="A87" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B87" s="10" t="s">
         <v>136</v>
       </c>
       <c r="C87" s="21" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D87" s="21"/>
       <c r="E87" s="21"/>
     </row>
     <row r="88">
       <c r="A88" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C88" s="21" t="s">
         <v>135</v>
@@ -3183,43 +3193,45 @@
       <c r="E88" s="21"/>
     </row>
     <row r="89">
-      <c r="A89" s="18">
+      <c r="A89" s="10">
+        <v>4</v>
+      </c>
+      <c r="B89" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C89" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="D89" s="21"/>
+      <c r="E89" s="21"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="18">
         <v>5</v>
       </c>
-      <c r="B89" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="C89" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="D89" s="19"/>
-      <c r="E89" s="19"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="10">
+      <c r="B90" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C90" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="D90" s="19"/>
+      <c r="E90" s="19"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="10">
         <v>6</v>
       </c>
-      <c r="B90" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="C90" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="D90" s="21"/>
-      <c r="E90" s="21"/>
-    </row>
-    <row r="91"/>
-    <row r="92">
-      <c r="A92" s="41" t="s">
+      <c r="B91" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="B92" s="41"/>
-      <c r="C92" s="41"/>
-      <c r="D92" s="41"/>
-      <c r="F92" s="42" t="s">
+      <c r="C91" s="21" t="s">
         <v>143</v>
       </c>
-    </row>
+      <c r="D91" s="21"/>
+      <c r="E91" s="21"/>
+    </row>
+    <row r="92"/>
     <row r="93">
       <c r="A93" s="41" t="s">
         <v>144</v>
@@ -3232,11 +3244,15 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="41"/>
+      <c r="A94" s="41" t="s">
+        <v>146</v>
+      </c>
       <c r="B94" s="41"/>
       <c r="C94" s="41"/>
       <c r="D94" s="41"/>
-      <c r="F94" s="43"/>
+      <c r="F94" s="42" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="41"/>
@@ -3266,77 +3282,66 @@
       <c r="D98" s="41"/>
       <c r="F98" s="43"/>
     </row>
-    <row r="99"/>
-    <row r="100">
-      <c r="A100" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B100" s="3"/>
-      <c r="C100" s="3"/>
-      <c r="D100" s="3"/>
-      <c r="E100" s="3"/>
-      <c r="F100" s="4"/>
-    </row>
+    <row r="99">
+      <c r="A99" s="41"/>
+      <c r="B99" s="41"/>
+      <c r="C99" s="41"/>
+      <c r="D99" s="41"/>
+      <c r="F99" s="43"/>
+    </row>
+    <row r="100"/>
     <row r="101">
-      <c r="A101" s="24"/>
-      <c r="B101" s="25" t="s">
+      <c r="A101" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="4"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="24"/>
+      <c r="B102" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C101" s="25" t="s">
+      <c r="C102" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="D101" s="25" t="s">
+      <c r="D102" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E101" s="25" t="s">
+      <c r="E102" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="F101" s="25" t="s">
+      <c r="F102" s="25" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="15" t="s">
+    <row r="103">
+      <c r="A103" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B102" s="10">
+      <c r="B103" s="10">
         <v>0</v>
       </c>
-      <c r="C102" s="10">
-        <v>1</v>
-      </c>
-      <c r="D102" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="E102" s="21" t="s">
+      <c r="C103" s="10">
+        <v>1</v>
+      </c>
+      <c r="D103" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="F102" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="15"/>
-      <c r="B103" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="C103" s="10">
-        <v>2</v>
-      </c>
-      <c r="D103" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E103" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="F103" s="10" t="s">
-        <v>148</v>
+      <c r="F103" s="21" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="15"/>
       <c r="B104" s="21" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C104" s="10">
         <v>2</v>
@@ -3345,70 +3350,62 @@
         <v>35</v>
       </c>
       <c r="E104" s="21" t="s">
-        <v>149</v>
+        <v>36</v>
       </c>
       <c r="F104" s="10" t="s">
         <v>150</v>
       </c>
     </row>
-    <row customHeight="true" ht="19" r="105">
+    <row r="105">
       <c r="A105" s="15"/>
       <c r="B105" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="C105" s="10">
+        <v>2</v>
+      </c>
+      <c r="D105" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E105" s="21" t="s">
         <v>151</v>
-      </c>
-      <c r="C105" s="10">
-        <v>1024</v>
-      </c>
-      <c r="D105" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="E105" s="21" t="s">
-        <v>23</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="s">
+    <row customHeight="true" ht="19" r="106">
+      <c r="A106" s="15"/>
+      <c r="B106" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="B106" s="3"/>
-      <c r="C106" s="3"/>
-      <c r="D106" s="3"/>
-      <c r="E106" s="3"/>
-      <c r="F106" s="4"/>
+      <c r="C106" s="10">
+        <v>1024</v>
+      </c>
+      <c r="D106" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E106" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="F106" s="10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="4"/>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="A74:A79"/>
-    <mergeCell ref="E75:E79"/>
-    <mergeCell ref="F75:F79"/>
-    <mergeCell ref="E55:E59"/>
-    <mergeCell ref="F55:F59"/>
-    <mergeCell ref="A54:A59"/>
-    <mergeCell ref="A63:A69"/>
-    <mergeCell ref="E46:E50"/>
-    <mergeCell ref="F46:F50"/>
-    <mergeCell ref="A45:A50"/>
     <mergeCell ref="A27:A32"/>
-    <mergeCell ref="F37:F41"/>
-    <mergeCell ref="C83:E83"/>
-    <mergeCell ref="C84:E84"/>
-    <mergeCell ref="C85:E85"/>
-    <mergeCell ref="C86:E86"/>
-    <mergeCell ref="C87:E87"/>
-    <mergeCell ref="C88:E88"/>
-    <mergeCell ref="C89:E89"/>
-    <mergeCell ref="C90:E90"/>
-    <mergeCell ref="H33:H48"/>
-    <mergeCell ref="L34:L40"/>
-    <mergeCell ref="L41:L47"/>
     <mergeCell ref="H30:H31"/>
-    <mergeCell ref="F93:F98"/>
-    <mergeCell ref="A92:D92"/>
-    <mergeCell ref="A93:D98"/>
     <mergeCell ref="L17:L20"/>
     <mergeCell ref="K17:K20"/>
     <mergeCell ref="J17:J20"/>
@@ -3423,7 +3420,32 @@
     <mergeCell ref="F18:F21"/>
     <mergeCell ref="A17:A22"/>
     <mergeCell ref="H14:H26"/>
-    <mergeCell ref="A102:A105"/>
+    <mergeCell ref="A103:A106"/>
+    <mergeCell ref="A94:D99"/>
+    <mergeCell ref="A93:D93"/>
+    <mergeCell ref="F94:F99"/>
+    <mergeCell ref="C91:E91"/>
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="C89:E89"/>
+    <mergeCell ref="C88:E88"/>
+    <mergeCell ref="C87:E87"/>
+    <mergeCell ref="C86:E86"/>
+    <mergeCell ref="C85:E85"/>
+    <mergeCell ref="C84:E84"/>
+    <mergeCell ref="A46:A51"/>
+    <mergeCell ref="F47:F51"/>
+    <mergeCell ref="E47:E51"/>
+    <mergeCell ref="A64:A70"/>
+    <mergeCell ref="A55:A60"/>
+    <mergeCell ref="F56:F60"/>
+    <mergeCell ref="E56:E60"/>
+    <mergeCell ref="F76:F80"/>
+    <mergeCell ref="E76:E80"/>
+    <mergeCell ref="A75:A80"/>
+    <mergeCell ref="L41:L47"/>
+    <mergeCell ref="L34:L40"/>
+    <mergeCell ref="H33:H48"/>
+    <mergeCell ref="A36:A42"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/doc/SOC-_MCU TCP报文.xlsx
+++ b/doc/SOC-_MCU TCP报文.xlsx
@@ -217,7 +217,7 @@
     <t xml:space="preserve">3~4</t>
   </si>
   <si>
-    <t xml:space="preserve">0x03 准备好OTA，本帧为单次脉冲，发送成功后清零</t>
+    <t xml:space="preserve">0x03 准备好OTA/ 0x0A 数据包正确/ 0x0B 数据包错误，本帧为单次脉冲，发送成功后清零</t>
   </si>
   <si>
     <t xml:space="preserve">5~6</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">Mode</t>
   </si>
   <si>
-    <t xml:space="preserve">0x01 OTA前查询/0x02 OTA全部发送完成后的通知</t>
+    <t xml:space="preserve">0x01 OTA前确认查询/0x02 OTA全部发送完成后的通知</t>
   </si>
   <si>
     <t xml:space="preserve">8~9</t>
@@ -847,6 +847,9 @@
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -861,9 +864,6 @@
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
@@ -1212,11 +1212,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="19"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" max="13" min="13" style="0" width="77"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" max="6" min="6" style="0" width="72"/>
     <col collapsed="false" customWidth="true" hidden="false" max="9" min="9" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" max="12" min="12" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="13" min="13" style="0" width="95"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1788,7 +1788,7 @@
       <c r="J20" s="10"/>
       <c r="K20" s="21"/>
       <c r="L20" s="26"/>
-      <c r="M20" s="7" t="s">
+      <c r="M20" s="29" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1807,19 +1807,19 @@
       <c r="F21" s="27"/>
       <c r="G21" s="5"/>
       <c r="H21" s="15"/>
-      <c r="I21" s="29">
+      <c r="I21" s="30">
         <v>9</v>
       </c>
-      <c r="J21" s="29">
-        <v>1</v>
-      </c>
-      <c r="K21" s="30" t="s">
+      <c r="J21" s="30">
+        <v>1</v>
+      </c>
+      <c r="K21" s="31" t="s">
         <v>11</v>
       </c>
       <c r="L21" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="M21" s="31" t="s">
+      <c r="M21" s="32" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="G23" s="32"/>
+      <c r="G23" s="33"/>
       <c r="H23" s="15"/>
       <c r="I23" s="21" t="s">
         <v>65</v>
@@ -1877,13 +1877,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="32"/>
-      <c r="B24" s="32"/>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
+      <c r="A24" s="33"/>
+      <c r="B24" s="33"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
       <c r="H24" s="15"/>
       <c r="I24" s="21" t="s">
         <v>67</v>
@@ -1910,7 +1910,7 @@
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="4"/>
-      <c r="G25" s="32"/>
+      <c r="G25" s="33"/>
       <c r="H25" s="15"/>
       <c r="I25" s="21" t="s">
         <v>70</v>
@@ -1924,8 +1924,8 @@
       <c r="L25" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="M25" s="33"/>
-      <c r="N25" s="32"/>
+      <c r="M25" s="34"/>
+      <c r="N25" s="33"/>
     </row>
     <row r="26">
       <c r="A26" s="24"/>
@@ -1944,7 +1944,7 @@
       <c r="F26" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="G26" s="32"/>
+      <c r="G26" s="33"/>
       <c r="H26" s="15"/>
       <c r="I26" s="21" t="s">
         <v>72</v>
@@ -1961,7 +1961,7 @@
       <c r="M26" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="N26" s="32"/>
+      <c r="N26" s="33"/>
     </row>
     <row r="27">
       <c r="A27" s="15" t="s">
@@ -1982,8 +1982,8 @@
       <c r="F27" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="G27" s="32"/>
-      <c r="N27" s="32"/>
+      <c r="G27" s="33"/>
+      <c r="N27" s="33"/>
     </row>
     <row r="28">
       <c r="A28" s="15"/>
@@ -2002,7 +2002,7 @@
       <c r="F28" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="G28" s="32"/>
+      <c r="G28" s="33"/>
       <c r="H28" s="6" t="s">
         <v>77</v>
       </c>
@@ -2011,7 +2011,7 @@
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="4"/>
-      <c r="N28" s="32"/>
+      <c r="N28" s="33"/>
     </row>
     <row r="29">
       <c r="A29" s="15"/>
@@ -2030,7 +2030,7 @@
       <c r="F29" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="G29" s="32"/>
+      <c r="G29" s="33"/>
       <c r="H29" s="7"/>
       <c r="I29" s="8" t="s">
         <v>5</v>
@@ -2047,7 +2047,7 @@
       <c r="M29" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="N29" s="32"/>
+      <c r="N29" s="33"/>
     </row>
     <row r="30">
       <c r="A30" s="15"/>
@@ -2066,7 +2066,7 @@
       <c r="F30" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="G30" s="32"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="9" t="s">
         <v>10</v>
       </c>
@@ -2085,7 +2085,7 @@
       <c r="M30" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N30" s="32"/>
+      <c r="N30" s="33"/>
     </row>
     <row r="31">
       <c r="A31" s="15"/>
@@ -2104,7 +2104,7 @@
       <c r="F31" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="G31" s="32"/>
+      <c r="G31" s="33"/>
       <c r="H31" s="9"/>
       <c r="I31" s="10">
         <v>1</v>
@@ -2121,7 +2121,7 @@
       <c r="M31" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="N31" s="32"/>
+      <c r="N31" s="33"/>
     </row>
     <row r="32">
       <c r="A32" s="15"/>
@@ -2140,7 +2140,7 @@
       <c r="F32" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="G32" s="32"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="13" t="s">
         <v>19</v>
       </c>
@@ -2159,15 +2159,15 @@
       <c r="M32" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="N32" s="32"/>
+      <c r="N32" s="33"/>
     </row>
     <row r="33">
-      <c r="A33" s="32"/>
-      <c r="B33" s="32"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="32"/>
+      <c r="A33" s="33"/>
+      <c r="B33" s="33"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
       <c r="H33" s="15" t="s">
         <v>23</v>
       </c>
@@ -2186,7 +2186,7 @@
       <c r="M33" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="N33" s="32"/>
+      <c r="N33" s="33"/>
     </row>
     <row customHeight="true" ht="19" r="34">
       <c r="A34" s="2" t="s">
@@ -2213,7 +2213,7 @@
       <c r="M34" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="N34" s="32"/>
+      <c r="N34" s="33"/>
     </row>
     <row customHeight="true" ht="19" r="35">
       <c r="A35" s="24"/>
@@ -2246,7 +2246,7 @@
       <c r="M35" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="N35" s="32"/>
+      <c r="N35" s="33"/>
     </row>
     <row customHeight="true" ht="19" r="36">
       <c r="A36" s="15" t="s">
@@ -2281,7 +2281,7 @@
       <c r="M36" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="N36" s="32"/>
+      <c r="N36" s="33"/>
     </row>
     <row customHeight="true" ht="19" r="37">
       <c r="A37" s="15"/>
@@ -2297,7 +2297,7 @@
       <c r="E37" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="F37" s="34" t="s">
+      <c r="F37" s="10" t="s">
         <v>93</v>
       </c>
       <c r="H37" s="15"/>
@@ -2314,7 +2314,7 @@
       <c r="M37" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="N37" s="32"/>
+      <c r="N37" s="33"/>
     </row>
     <row customHeight="true" ht="19" r="38">
       <c r="A38" s="15"/>
@@ -2328,7 +2328,9 @@
         <v>11</v>
       </c>
       <c r="E38" s="21"/>
-      <c r="F38" s="27"/>
+      <c r="F38" s="27" t="s">
+        <v>53</v>
+      </c>
       <c r="H38" s="15"/>
       <c r="I38" s="10" t="s">
         <v>96</v>
@@ -2343,7 +2345,7 @@
       <c r="M38" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="N38" s="32"/>
+      <c r="N38" s="33"/>
     </row>
     <row customHeight="true" ht="19" r="39">
       <c r="A39" s="15"/>
@@ -2372,7 +2374,7 @@
       <c r="M39" s="35" t="s">
         <v>99</v>
       </c>
-      <c r="N39" s="32"/>
+      <c r="N39" s="33"/>
     </row>
     <row customHeight="true" ht="19" r="40">
       <c r="A40" s="15"/>
@@ -2401,7 +2403,7 @@
       <c r="M40" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="N40" s="32"/>
+      <c r="N40" s="33"/>
     </row>
     <row customHeight="true" ht="19" r="41">
       <c r="A41" s="15"/>
@@ -2432,7 +2434,7 @@
       <c r="M41" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="N41" s="32"/>
+      <c r="N41" s="33"/>
     </row>
     <row customHeight="true" ht="19" r="42">
       <c r="A42" s="15"/>
@@ -2461,7 +2463,7 @@
       <c r="M42" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="N42" s="32"/>
+      <c r="N42" s="33"/>
     </row>
     <row customHeight="true" ht="19" r="43">
       <c r="H43" s="15"/>
@@ -2478,7 +2480,7 @@
       <c r="M43" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="N43" s="32"/>
+      <c r="N43" s="33"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
@@ -2489,7 +2491,7 @@
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
       <c r="F44" s="4"/>
-      <c r="G44" s="32"/>
+      <c r="G44" s="33"/>
       <c r="H44" s="15"/>
       <c r="I44" s="10" t="s">
         <v>104</v>
@@ -2504,7 +2506,7 @@
       <c r="M44" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="N44" s="32"/>
+      <c r="N44" s="33"/>
     </row>
     <row r="45">
       <c r="A45" s="24"/>
@@ -2537,7 +2539,7 @@
       <c r="M45" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="N45" s="32"/>
+      <c r="N45" s="33"/>
     </row>
     <row r="46">
       <c r="A46" s="15" t="s">
@@ -2572,7 +2574,7 @@
       <c r="M46" s="35" t="s">
         <v>99</v>
       </c>
-      <c r="N46" s="32"/>
+      <c r="N46" s="33"/>
     </row>
     <row r="47">
       <c r="A47" s="15"/>
@@ -2602,10 +2604,10 @@
         <v>11</v>
       </c>
       <c r="L47" s="21"/>
-      <c r="M47" s="29" t="s">
+      <c r="M47" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="N47" s="32"/>
+      <c r="N47" s="33"/>
     </row>
     <row r="48">
       <c r="A48" s="15"/>
@@ -2627,14 +2629,14 @@
       <c r="J48" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="K48" s="33"/>
+      <c r="K48" s="34"/>
       <c r="L48" s="21" t="s">
         <v>110</v>
       </c>
       <c r="M48" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="N48" s="32"/>
+      <c r="N48" s="33"/>
     </row>
     <row r="49">
       <c r="A49" s="15"/>
@@ -2649,7 +2651,7 @@
       </c>
       <c r="E49" s="27"/>
       <c r="F49" s="27"/>
-      <c r="N49" s="32"/>
+      <c r="N49" s="33"/>
     </row>
     <row r="50">
       <c r="A50" s="15"/>
@@ -2664,11 +2666,11 @@
       </c>
       <c r="E50" s="27"/>
       <c r="F50" s="27"/>
-      <c r="I50" s="32"/>
-      <c r="J50" s="32"/>
-      <c r="K50" s="32"/>
-      <c r="L50" s="32"/>
-      <c r="M50" s="32"/>
+      <c r="I50" s="33"/>
+      <c r="J50" s="33"/>
+      <c r="K50" s="33"/>
+      <c r="L50" s="33"/>
+      <c r="M50" s="33"/>
     </row>
     <row r="51">
       <c r="A51" s="15"/>
@@ -2685,12 +2687,12 @@
       <c r="F51" s="27"/>
     </row>
     <row r="52">
-      <c r="A52" s="32"/>
-      <c r="B52" s="32"/>
-      <c r="C52" s="32"/>
-      <c r="D52" s="32"/>
-      <c r="E52" s="32"/>
-      <c r="F52" s="32"/>
+      <c r="A52" s="33"/>
+      <c r="B52" s="33"/>
+      <c r="C52" s="33"/>
+      <c r="D52" s="33"/>
+      <c r="E52" s="33"/>
+      <c r="F52" s="33"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
@@ -2975,11 +2977,11 @@
       <c r="A71" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="B71" s="33"/>
-      <c r="C71" s="33"/>
-      <c r="D71" s="33"/>
-      <c r="E71" s="33"/>
-      <c r="F71" s="33"/>
+      <c r="B71" s="34"/>
+      <c r="C71" s="34"/>
+      <c r="D71" s="34"/>
+      <c r="E71" s="34"/>
+      <c r="F71" s="34"/>
     </row>
     <row customHeight="true" ht="19" r="72"/>
     <row r="73">
@@ -3009,7 +3011,7 @@
       <c r="F74" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="N74" s="32"/>
+      <c r="N74" s="33"/>
     </row>
     <row r="75">
       <c r="A75" s="15" t="s">
@@ -3030,7 +3032,7 @@
       <c r="F75" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="N75" s="32"/>
+      <c r="N75" s="33"/>
     </row>
     <row r="76">
       <c r="A76" s="15"/>
@@ -3138,7 +3140,7 @@
       </c>
       <c r="D84" s="40"/>
       <c r="E84" s="40"/>
-      <c r="N84" s="32"/>
+      <c r="N84" s="33"/>
     </row>
     <row r="85">
       <c r="A85" s="10">
@@ -3404,19 +3406,9 @@
     </row>
   </sheetData>
   <mergeCells>
+    <mergeCell ref="I17:I20"/>
     <mergeCell ref="A27:A32"/>
     <mergeCell ref="H30:H31"/>
-    <mergeCell ref="L17:L20"/>
-    <mergeCell ref="K17:K20"/>
-    <mergeCell ref="J17:J20"/>
-    <mergeCell ref="I17:I20"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="H11:H12"/>
     <mergeCell ref="F18:F21"/>
     <mergeCell ref="A17:A22"/>
     <mergeCell ref="H14:H26"/>
@@ -3446,6 +3438,17 @@
     <mergeCell ref="L34:L40"/>
     <mergeCell ref="H33:H48"/>
     <mergeCell ref="A36:A42"/>
+    <mergeCell ref="F38:F42"/>
+    <mergeCell ref="J17:J20"/>
+    <mergeCell ref="K17:K20"/>
+    <mergeCell ref="L17:L20"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="H11:H12"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
